--- a/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADG.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADG.xlsx
@@ -1115,13 +1115,13 @@
         <v>72.40000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -1134,13 +1134,13 @@
         <v>100.9</v>
       </c>
       <c r="C3" t="n">
-        <v>97.8</v>
+        <v>97.3</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
@@ -1153,13 +1153,13 @@
         <v>98.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1172,13 +1172,13 @@
         <v>2.9</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1191,13 +1191,13 @@
         <v>15.5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1216,7 @@
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1232,7 +1232,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1248,13 +1248,13 @@
         <v>23.5</v>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="n">
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
